--- a/LLRF3_HTR/C75_HTR_MBP_HRT.xlsx
+++ b/LLRF3_HTR/C75_HTR_MBP_HRT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\geesamen\Documents\GitProjects\EES_REPO_CTRL\LLRF3_HTR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0E061F-BB31-4CE7-A39D-7A51E2402536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF91F69-7E16-4C6B-B904-4327CA477B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="105" yWindow="2040" windowWidth="28695" windowHeight="15240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="4440" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="Register_Detail" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="443">
   <si>
     <t>Description</t>
   </si>
@@ -1360,6 +1359,12 @@
   </si>
   <si>
     <t>DAC Setpoint</t>
+  </si>
+  <si>
+    <t>RSTR</t>
+  </si>
+  <si>
+    <t>Restore Status</t>
   </si>
 </sst>
 </file>
@@ -2175,8 +2180,12 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="B10" s="4"/>
+      <c r="A10" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>441</v>
+      </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -2197,9 +2206,11 @@
         <f t="shared" si="2"/>
         <v>000001110</v>
       </c>
-      <c r="H10" s="4"/>
+      <c r="H10" s="4" t="s">
+        <v>442</v>
+      </c>
       <c r="I10" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>10</v>
@@ -5601,7 +5612,7 @@
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>CONCATENATE("{ """,Table!A10,""",",IF(LEN(Table!A10)=0,"   ",IF(LEN(Table!A10)=1,"  "," ")),"""",Table!B10,""",",IF(LEN(Table!B10)=0,"       ",IF(LEN(Table!B10)=1,"      ",IF(LEN(Table!B10)=2,"     ",IF(LEN(Table!B10)=3,"    ",IF(LEN(Table!B10)=4,"   ",IF(LEN(Table!B10)=5,"  "," ")))))),"0x",Table!F10,", ",Table!J10,",",IF(OR((Table!J10="U16"),(Table!J10="S16")),"  "," "),Table!I10,", ",Table!K10,IF(Table!C10&lt;10,", ""  ",IF(Table!C10&lt;100,", "" ",", """)),Table!C10," ",Table!H10,""" },")</f>
-        <v>{ "",   "",       0x000E, U16,  RO, CSX, "  7 " },</v>
+        <v>{ "HTR", "RSTR",   0x000E, U16,  RW, CSX, "  7 Restore Status" },</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -6251,7 +6262,7 @@
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>IF(Table!I10="RO",CONCATENATE("     reg_ena","(",Table!D10,")"," &lt;= '1';","   ","reg_d(",Table!D10,") &lt;= x""FFFF"";"),CONCATENATE("     reg_ena","(",Table!D10,")"," &lt;= '1' when (LOAD = '1') and (shrt_addr = x""",DEC2HEX(Table!D10,2),""")"," else '0';","   ","reg_d(",Table!D10,") &lt;= DIN;"))</f>
-        <v xml:space="preserve">     reg_ena(7) &lt;= '1';   reg_d(7) &lt;= x"FFFF";</v>
+        <v xml:space="preserve">     reg_ena(7) &lt;= '1' when (LOAD = '1') and (shrt_addr = x"07") else '0';   reg_d(7) &lt;= DIN;</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">

--- a/LLRF3_HTR/C75_HTR_MBP_HRT.xlsx
+++ b/LLRF3_HTR/C75_HTR_MBP_HRT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\geesamen\Documents\GitProjects\EES_REPO_CTRL\LLRF3_HTR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF91F69-7E16-4C6B-B904-4327CA477B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F36FED4-B6CC-47E5-97E7-0266A2E7138F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="4440" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5355" yWindow="5595" windowWidth="28695" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="445">
   <si>
     <t>Description</t>
   </si>
@@ -1365,6 +1365,12 @@
   </si>
   <si>
     <t>Restore Status</t>
+  </si>
+  <si>
+    <t>HB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heartbeat </t>
   </si>
 </sst>
 </file>
@@ -2220,8 +2226,12 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="4"/>
+      <c r="A11" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>443</v>
+      </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -2242,12 +2252,14 @@
         <f t="shared" si="2"/>
         <v>000010000</v>
       </c>
-      <c r="H11" s="4"/>
+      <c r="H11" s="4" t="s">
+        <v>444</v>
+      </c>
       <c r="I11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>15</v>
@@ -5618,7 +5630,7 @@
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>CONCATENATE("{ """,Table!A11,""",",IF(LEN(Table!A11)=0,"   ",IF(LEN(Table!A11)=1,"  "," ")),"""",Table!B11,""",",IF(LEN(Table!B11)=0,"       ",IF(LEN(Table!B11)=1,"      ",IF(LEN(Table!B11)=2,"     ",IF(LEN(Table!B11)=3,"    ",IF(LEN(Table!B11)=4,"   ",IF(LEN(Table!B11)=5,"  "," ")))))),"0x",Table!F11,", ",Table!J11,",",IF(OR((Table!J11="U16"),(Table!J11="S16")),"  "," "),Table!I11,", ",Table!K11,IF(Table!C11&lt;10,", ""  ",IF(Table!C11&lt;100,", "" ",", """)),Table!C11," ",Table!H11,""" },")</f>
-        <v>{ "",   "",       0x0010, S16,  RO, CSX, "  8 " },</v>
+        <v>{ "HTR", "HB",     0x0010, U16,  RO, CSX, "  8 Heartbeat " },</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
